--- a/veterinarian_forms/007_sick_pet_appointment_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/007_sick_pet_appointment_form--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dr._smith'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dr. Smith'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dr._johnson'}</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dr. Johnson'}</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr._thompson'}</t>
+          <t>dr._thompson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr. Thompson'}</t>
+          <t>Dr. Thompson</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'arthritis'}</t>
+          <t>arthritis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Arthritis'}</t>
+          <t>Arthritis</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'form_submitter'}</t>
+          <t>form_submitter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Form Submitter'}</t>
+          <t>Form Submitter</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'owner'}</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Owner'}</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
